--- a/astro-site/public/dl/restaurant-financial-plan-templates/BONUS-09-pre-opening-financial-checklist.xlsx
+++ b/astro-site/public/dl/restaurant-financial-plan-templates/BONUS-09-pre-opening-financial-checklist.xlsx
@@ -221,7 +221,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -279,8 +279,17 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="7" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
@@ -689,7 +698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B28"/>
+  <dimension ref="A2:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -829,6 +838,20 @@
       <c r="B28" s="21" t="inlineStr">
         <is>
           <t>Version 2.0 · October 2026 · aichef.pro/en/digital-products/restaurant-financial-plan-templates · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="B29" s="40" t="inlineStr">
+        <is>
+          <t>Planning tool, not financial, tax or legal advice. Requirements vary by state and city — check with your accountant and local authorities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="40" t="inlineStr">
+        <is>
+          <t>This checklist is a starting point, not an exhaustive list.</t>
         </is>
       </c>
     </row>
@@ -917,7 +940,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="n">
         <v>1</v>
       </c>
@@ -926,13 +949,13 @@
           <t>1. Formation</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="41" t="inlineStr">
         <is>
           <t>Choose the legal entity (LLC, S corp, C corp or sole proprietorship)</t>
         </is>
       </c>
       <c r="D5" s="23" t="n"/>
-      <c r="E5" s="40" t="n"/>
+      <c r="E5" s="42" t="n"/>
       <c r="F5" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -940,7 +963,7 @@
       </c>
       <c r="G5" s="23" t="n"/>
     </row>
-    <row r="6">
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="7" t="n">
         <v>2</v>
       </c>
@@ -949,13 +972,13 @@
           <t>1. Formation</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="41" t="inlineStr">
         <is>
           <t>File the articles of organization or incorporation with the state</t>
         </is>
       </c>
       <c r="D6" s="23" t="n"/>
-      <c r="E6" s="40" t="n"/>
+      <c r="E6" s="42" t="n"/>
       <c r="F6" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -963,7 +986,7 @@
       </c>
       <c r="G6" s="23" t="n"/>
     </row>
-    <row r="7">
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="7" t="n">
         <v>3</v>
       </c>
@@ -972,13 +995,13 @@
           <t>1. Formation</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="41" t="inlineStr">
         <is>
           <t>Register a DBA (assumed name) if you trade under another name</t>
         </is>
       </c>
       <c r="D7" s="23" t="n"/>
-      <c r="E7" s="40" t="n"/>
+      <c r="E7" s="42" t="n"/>
       <c r="F7" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -995,13 +1018,13 @@
           <t>1. Formation</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="41" t="inlineStr">
         <is>
           <t>Get your EIN from the IRS (free, online)</t>
         </is>
       </c>
       <c r="D8" s="23" t="n"/>
-      <c r="E8" s="40" t="n"/>
+      <c r="E8" s="42" t="n"/>
       <c r="F8" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1018,13 +1041,13 @@
           <t>1. Formation</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="41" t="inlineStr">
         <is>
           <t>Open a business bank account</t>
         </is>
       </c>
       <c r="D9" s="23" t="n"/>
-      <c r="E9" s="40" t="n"/>
+      <c r="E9" s="42" t="n"/>
       <c r="F9" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1032,7 +1055,7 @@
       </c>
       <c r="G9" s="23" t="n"/>
     </row>
-    <row r="10">
+    <row r="10" ht="30" customHeight="1">
       <c r="A10" s="7" t="n">
         <v>6</v>
       </c>
@@ -1041,13 +1064,13 @@
           <t>1. Formation</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="41" t="inlineStr">
         <is>
           <t>Operating agreement or bylaws, and ownership records</t>
         </is>
       </c>
       <c r="D10" s="23" t="n"/>
-      <c r="E10" s="40" t="n"/>
+      <c r="E10" s="42" t="n"/>
       <c r="F10" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1055,7 +1078,7 @@
       </c>
       <c r="G10" s="23" t="n"/>
     </row>
-    <row r="11">
+    <row r="11" ht="30" customHeight="1">
       <c r="A11" s="7" t="n">
         <v>7</v>
       </c>
@@ -1064,13 +1087,13 @@
           <t>1. Formation</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="41" t="inlineStr">
         <is>
           <t>Register with the state tax agency (sales tax / seller's permit)</t>
         </is>
       </c>
       <c r="D11" s="23" t="n"/>
-      <c r="E11" s="40" t="n"/>
+      <c r="E11" s="42" t="n"/>
       <c r="F11" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1087,13 +1110,13 @@
           <t>1. Formation</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="41" t="inlineStr">
         <is>
           <t>Trademark search and registration (USPTO)</t>
         </is>
       </c>
       <c r="D12" s="23" t="n"/>
-      <c r="E12" s="40" t="n"/>
+      <c r="E12" s="42" t="n"/>
       <c r="F12" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1110,13 +1133,13 @@
           <t>2. Financing</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="41" t="inlineStr">
         <is>
           <t>Prepare a complete financial plan</t>
         </is>
       </c>
       <c r="D13" s="23" t="n"/>
-      <c r="E13" s="40" t="n"/>
+      <c r="E13" s="42" t="n"/>
       <c r="F13" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1133,13 +1156,13 @@
           <t>2. Financing</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="41" t="inlineStr">
         <is>
           <t>Calculate investment needs (capex)</t>
         </is>
       </c>
       <c r="D14" s="23" t="n"/>
-      <c r="E14" s="40" t="n"/>
+      <c r="E14" s="42" t="n"/>
       <c r="F14" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1147,7 +1170,7 @@
       </c>
       <c r="G14" s="23" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="30" customHeight="1">
       <c r="A15" s="7" t="n">
         <v>11</v>
       </c>
@@ -1156,13 +1179,13 @@
           <t>2. Financing</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="41" t="inlineStr">
         <is>
           <t>Determine the working capital needed (3-6 months)</t>
         </is>
       </c>
       <c r="D15" s="23" t="n"/>
-      <c r="E15" s="40" t="n"/>
+      <c r="E15" s="42" t="n"/>
       <c r="F15" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1170,7 +1193,7 @@
       </c>
       <c r="G15" s="23" t="n"/>
     </row>
-    <row r="16">
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" s="7" t="n">
         <v>12</v>
       </c>
@@ -1179,13 +1202,13 @@
           <t>2. Financing</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="41" t="inlineStr">
         <is>
           <t>Apply for an SBA 7(a) loan or a line of credit</t>
         </is>
       </c>
       <c r="D16" s="23" t="n"/>
-      <c r="E16" s="40" t="n"/>
+      <c r="E16" s="42" t="n"/>
       <c r="F16" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1202,13 +1225,13 @@
           <t>2. Financing</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="41" t="inlineStr">
         <is>
           <t>Look for state and local grants or incentives</t>
         </is>
       </c>
       <c r="D17" s="23" t="n"/>
-      <c r="E17" s="40" t="n"/>
+      <c r="E17" s="42" t="n"/>
       <c r="F17" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1225,13 +1248,13 @@
           <t>2. Financing</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="41" t="inlineStr">
         <is>
           <t>Pitch the project to private investors</t>
         </is>
       </c>
       <c r="D18" s="23" t="n"/>
-      <c r="E18" s="40" t="n"/>
+      <c r="E18" s="42" t="n"/>
       <c r="F18" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1239,7 +1262,7 @@
       </c>
       <c r="G18" s="23" t="n"/>
     </row>
-    <row r="19">
+    <row r="19" ht="30" customHeight="1">
       <c r="A19" s="7" t="n">
         <v>15</v>
       </c>
@@ -1248,13 +1271,13 @@
           <t>2. Financing</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="41" t="inlineStr">
         <is>
           <t>Negotiate loan terms (rate, term, interest-only period)</t>
         </is>
       </c>
       <c r="D19" s="23" t="n"/>
-      <c r="E19" s="40" t="n"/>
+      <c r="E19" s="42" t="n"/>
       <c r="F19" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1271,13 +1294,13 @@
           <t>2. Financing</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="41" t="inlineStr">
         <is>
           <t>Sign the financing agreements</t>
         </is>
       </c>
       <c r="D20" s="23" t="n"/>
-      <c r="E20" s="40" t="n"/>
+      <c r="E20" s="42" t="n"/>
       <c r="F20" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1294,13 +1317,13 @@
           <t>3. Licenses &amp; Permits</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="41" t="inlineStr">
         <is>
           <t>Business license and certificate of occupancy</t>
         </is>
       </c>
       <c r="D21" s="23" t="n"/>
-      <c r="E21" s="40" t="n"/>
+      <c r="E21" s="42" t="n"/>
       <c r="F21" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1317,13 +1340,13 @@
           <t>3. Licenses &amp; Permits</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="41" t="inlineStr">
         <is>
           <t>Building permits (if you renovate)</t>
         </is>
       </c>
       <c r="D22" s="23" t="n"/>
-      <c r="E22" s="40" t="n"/>
+      <c r="E22" s="42" t="n"/>
       <c r="F22" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1340,13 +1363,13 @@
           <t>3. Licenses &amp; Permits</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="41" t="inlineStr">
         <is>
           <t>Architect / engineer drawings for the permits</t>
         </is>
       </c>
       <c r="D23" s="23" t="n"/>
-      <c r="E23" s="40" t="n"/>
+      <c r="E23" s="42" t="n"/>
       <c r="F23" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1363,13 +1386,13 @@
           <t>3. Licenses &amp; Permits</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C24" s="41" t="inlineStr">
         <is>
           <t>Fire department inspection and occupancy load</t>
         </is>
       </c>
       <c r="D24" s="23" t="n"/>
-      <c r="E24" s="40" t="n"/>
+      <c r="E24" s="42" t="n"/>
       <c r="F24" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1377,7 +1400,7 @@
       </c>
       <c r="G24" s="23" t="n"/>
     </row>
-    <row r="25">
+    <row r="25" ht="30" customHeight="1">
       <c r="A25" s="7" t="n">
         <v>21</v>
       </c>
@@ -1386,13 +1409,13 @@
           <t>3. Licenses &amp; Permits</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C25" s="41" t="inlineStr">
         <is>
           <t>Health department plan review and food service permit</t>
         </is>
       </c>
       <c r="D25" s="23" t="n"/>
-      <c r="E25" s="40" t="n"/>
+      <c r="E25" s="42" t="n"/>
       <c r="F25" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1400,7 +1423,7 @@
       </c>
       <c r="G25" s="23" t="n"/>
     </row>
-    <row r="26">
+    <row r="26" ht="30" customHeight="1">
       <c r="A26" s="7" t="n">
         <v>22</v>
       </c>
@@ -1409,13 +1432,13 @@
           <t>3. Licenses &amp; Permits</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C26" s="41" t="inlineStr">
         <is>
           <t>Liquor license (apply early: it can take months)</t>
         </is>
       </c>
       <c r="D26" s="23" t="n"/>
-      <c r="E26" s="40" t="n"/>
+      <c r="E26" s="42" t="n"/>
       <c r="F26" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1423,7 +1446,7 @@
       </c>
       <c r="G26" s="23" t="n"/>
     </row>
-    <row r="27">
+    <row r="27" ht="30" customHeight="1">
       <c r="A27" s="7" t="n">
         <v>23</v>
       </c>
@@ -1432,13 +1455,13 @@
           <t>3. Licenses &amp; Permits</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C27" s="41" t="inlineStr">
         <is>
           <t>Sign permit and sidewalk seating permit (if any)</t>
         </is>
       </c>
       <c r="D27" s="23" t="n"/>
-      <c r="E27" s="40" t="n"/>
+      <c r="E27" s="42" t="n"/>
       <c r="F27" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1446,7 +1469,7 @@
       </c>
       <c r="G27" s="23" t="n"/>
     </row>
-    <row r="28">
+    <row r="28" ht="30" customHeight="1">
       <c r="A28" s="7" t="n">
         <v>24</v>
       </c>
@@ -1455,13 +1478,13 @@
           <t>3. Licenses &amp; Permits</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C28" s="41" t="inlineStr">
         <is>
           <t>Waste, recycling and grease trap service contracts</t>
         </is>
       </c>
       <c r="D28" s="23" t="n"/>
-      <c r="E28" s="40" t="n"/>
+      <c r="E28" s="42" t="n"/>
       <c r="F28" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1478,13 +1501,13 @@
           <t>4. Suppliers</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C29" s="41" t="inlineStr">
         <is>
           <t>Select the main food distributor</t>
         </is>
       </c>
       <c r="D29" s="23" t="n"/>
-      <c r="E29" s="40" t="n"/>
+      <c r="E29" s="42" t="n"/>
       <c r="F29" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1492,7 +1515,7 @@
       </c>
       <c r="G29" s="23" t="n"/>
     </row>
-    <row r="30">
+    <row r="30" ht="30" customHeight="1">
       <c r="A30" s="7" t="n">
         <v>26</v>
       </c>
@@ -1501,13 +1524,13 @@
           <t>4. Suppliers</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C30" s="41" t="inlineStr">
         <is>
           <t>Set up utility service (electricity, water, gas)</t>
         </is>
       </c>
       <c r="D30" s="23" t="n"/>
-      <c r="E30" s="40" t="n"/>
+      <c r="E30" s="42" t="n"/>
       <c r="F30" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1524,13 +1547,13 @@
           <t>4. Suppliers</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C31" s="41" t="inlineStr">
         <is>
           <t>Negotiate the lease and security deposit</t>
         </is>
       </c>
       <c r="D31" s="23" t="n"/>
-      <c r="E31" s="40" t="n"/>
+      <c r="E31" s="42" t="n"/>
       <c r="F31" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1547,13 +1570,13 @@
           <t>4. Suppliers</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C32" s="41" t="inlineStr">
         <is>
           <t>Contract a laundry / linen service</t>
         </is>
       </c>
       <c r="D32" s="23" t="n"/>
-      <c r="E32" s="40" t="n"/>
+      <c r="E32" s="42" t="n"/>
       <c r="F32" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1570,13 +1593,13 @@
           <t>4. Suppliers</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C33" s="41" t="inlineStr">
         <is>
           <t>Contract equipment maintenance</t>
         </is>
       </c>
       <c r="D33" s="23" t="n"/>
-      <c r="E33" s="40" t="n"/>
+      <c r="E33" s="42" t="n"/>
       <c r="F33" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1593,13 +1616,13 @@
           <t>4. Suppliers</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C34" s="41" t="inlineStr">
         <is>
           <t>Hire a licensed pest control service</t>
         </is>
       </c>
       <c r="D34" s="23" t="n"/>
-      <c r="E34" s="40" t="n"/>
+      <c r="E34" s="42" t="n"/>
       <c r="F34" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1616,13 +1639,13 @@
           <t>4. Suppliers</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C35" s="41" t="inlineStr">
         <is>
           <t>Sign agreements with delivery platforms</t>
         </is>
       </c>
       <c r="D35" s="23" t="n"/>
-      <c r="E35" s="40" t="n"/>
+      <c r="E35" s="42" t="n"/>
       <c r="F35" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1639,13 +1662,13 @@
           <t>4. Suppliers</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C36" s="41" t="inlineStr">
         <is>
           <t>Negotiate payment terms with key suppliers</t>
         </is>
       </c>
       <c r="D36" s="23" t="n"/>
-      <c r="E36" s="40" t="n"/>
+      <c r="E36" s="42" t="n"/>
       <c r="F36" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1662,13 +1685,13 @@
           <t>5. Insurance</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C37" s="41" t="inlineStr">
         <is>
           <t>General liability insurance</t>
         </is>
       </c>
       <c r="D37" s="23" t="n"/>
-      <c r="E37" s="40" t="n"/>
+      <c r="E37" s="42" t="n"/>
       <c r="F37" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1685,13 +1708,13 @@
           <t>5. Insurance</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="C38" s="41" t="inlineStr">
         <is>
           <t>Commercial property insurance (or a BOP)</t>
         </is>
       </c>
       <c r="D38" s="23" t="n"/>
-      <c r="E38" s="40" t="n"/>
+      <c r="E38" s="42" t="n"/>
       <c r="F38" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1699,7 +1722,7 @@
       </c>
       <c r="G38" s="23" t="n"/>
     </row>
-    <row r="39">
+    <row r="39" ht="30" customHeight="1">
       <c r="A39" s="7" t="n">
         <v>35</v>
       </c>
@@ -1708,13 +1731,13 @@
           <t>5. Insurance</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C39" s="41" t="inlineStr">
         <is>
           <t>Workers' compensation insurance (required in most states)</t>
         </is>
       </c>
       <c r="D39" s="23" t="n"/>
-      <c r="E39" s="40" t="n"/>
+      <c r="E39" s="42" t="n"/>
       <c r="F39" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1731,13 +1754,13 @@
           <t>5. Insurance</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="C40" s="41" t="inlineStr">
         <is>
           <t>Business interruption insurance</t>
         </is>
       </c>
       <c r="D40" s="23" t="n"/>
-      <c r="E40" s="40" t="n"/>
+      <c r="E40" s="42" t="n"/>
       <c r="F40" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1745,7 +1768,7 @@
       </c>
       <c r="G40" s="23" t="n"/>
     </row>
-    <row r="41">
+    <row r="41" ht="30" customHeight="1">
       <c r="A41" s="7" t="n">
         <v>37</v>
       </c>
@@ -1754,13 +1777,13 @@
           <t>5. Insurance</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C41" s="41" t="inlineStr">
         <is>
           <t>Food spoilage and equipment breakdown coverage</t>
         </is>
       </c>
       <c r="D41" s="23" t="n"/>
-      <c r="E41" s="40" t="n"/>
+      <c r="E41" s="42" t="n"/>
       <c r="F41" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1768,7 +1791,7 @@
       </c>
       <c r="G41" s="23" t="n"/>
     </row>
-    <row r="42">
+    <row r="42" ht="30" customHeight="1">
       <c r="A42" s="7" t="n">
         <v>38</v>
       </c>
@@ -1777,13 +1800,13 @@
           <t>5. Insurance</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr">
+      <c r="C42" s="41" t="inlineStr">
         <is>
           <t>Liquor liability insurance (if you serve alcohol)</t>
         </is>
       </c>
       <c r="D42" s="23" t="n"/>
-      <c r="E42" s="40" t="n"/>
+      <c r="E42" s="42" t="n"/>
       <c r="F42" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1791,7 +1814,7 @@
       </c>
       <c r="G42" s="23" t="n"/>
     </row>
-    <row r="43">
+    <row r="43" ht="30" customHeight="1">
       <c r="A43" s="7" t="n">
         <v>39</v>
       </c>
@@ -1800,13 +1823,13 @@
           <t>5. Insurance</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C43" s="41" t="inlineStr">
         <is>
           <t>Cyber liability insurance (POS and online orders)</t>
         </is>
       </c>
       <c r="D43" s="23" t="n"/>
-      <c r="E43" s="40" t="n"/>
+      <c r="E43" s="42" t="n"/>
       <c r="F43" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1814,7 +1837,7 @@
       </c>
       <c r="G43" s="23" t="n"/>
     </row>
-    <row r="44">
+    <row r="44" ht="30" customHeight="1">
       <c r="A44" s="7" t="n">
         <v>40</v>
       </c>
@@ -1823,13 +1846,13 @@
           <t>5. Insurance</t>
         </is>
       </c>
-      <c r="C44" s="9" t="inlineStr">
+      <c r="C44" s="41" t="inlineStr">
         <is>
           <t>Surety bond (if your state or a license requires one)</t>
         </is>
       </c>
       <c r="D44" s="23" t="n"/>
-      <c r="E44" s="40" t="n"/>
+      <c r="E44" s="42" t="n"/>
       <c r="F44" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1846,13 +1869,13 @@
           <t>6. Cash Management</t>
         </is>
       </c>
-      <c r="C45" s="9" t="inlineStr">
+      <c r="C45" s="41" t="inlineStr">
         <is>
           <t>Set up the POS and card terminals</t>
         </is>
       </c>
       <c r="D45" s="23" t="n"/>
-      <c r="E45" s="40" t="n"/>
+      <c r="E45" s="42" t="n"/>
       <c r="F45" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1869,13 +1892,13 @@
           <t>6. Cash Management</t>
         </is>
       </c>
-      <c r="C46" s="9" t="inlineStr">
+      <c r="C46" s="41" t="inlineStr">
         <is>
           <t>Activate the online payment gateway</t>
         </is>
       </c>
       <c r="D46" s="23" t="n"/>
-      <c r="E46" s="40" t="n"/>
+      <c r="E46" s="42" t="n"/>
       <c r="F46" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1883,7 +1906,7 @@
       </c>
       <c r="G46" s="23" t="n"/>
     </row>
-    <row r="47">
+    <row r="47" ht="30" customHeight="1">
       <c r="A47" s="7" t="n">
         <v>43</v>
       </c>
@@ -1892,13 +1915,13 @@
           <t>6. Cash Management</t>
         </is>
       </c>
-      <c r="C47" s="9" t="inlineStr">
+      <c r="C47" s="41" t="inlineStr">
         <is>
           <t>Set up accounting software and sales tax reporting</t>
         </is>
       </c>
       <c r="D47" s="23" t="n"/>
-      <c r="E47" s="40" t="n"/>
+      <c r="E47" s="42" t="n"/>
       <c r="F47" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1915,13 +1938,13 @@
           <t>6. Cash Management</t>
         </is>
       </c>
-      <c r="C48" s="9" t="inlineStr">
+      <c r="C48" s="41" t="inlineStr">
         <is>
           <t>Set the cash float (opening cash)</t>
         </is>
       </c>
       <c r="D48" s="23" t="n"/>
-      <c r="E48" s="40" t="n"/>
+      <c r="E48" s="42" t="n"/>
       <c r="F48" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1929,7 +1952,7 @@
       </c>
       <c r="G48" s="23" t="n"/>
     </row>
-    <row r="49">
+    <row r="49" ht="30" customHeight="1">
       <c r="A49" s="7" t="n">
         <v>45</v>
       </c>
@@ -1938,13 +1961,13 @@
           <t>6. Cash Management</t>
         </is>
       </c>
-      <c r="C49" s="9" t="inlineStr">
+      <c r="C49" s="41" t="inlineStr">
         <is>
           <t>Define the tip policy (tip pooling and tip credit rules)</t>
         </is>
       </c>
       <c r="D49" s="23" t="n"/>
-      <c r="E49" s="40" t="n"/>
+      <c r="E49" s="42" t="n"/>
       <c r="F49" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1961,13 +1984,13 @@
           <t>6. Cash Management</t>
         </is>
       </c>
-      <c r="C50" s="9" t="inlineStr">
+      <c r="C50" s="41" t="inlineStr">
         <is>
           <t>Set up autopay (rent, utilities)</t>
         </is>
       </c>
       <c r="D50" s="23" t="n"/>
-      <c r="E50" s="40" t="n"/>
+      <c r="E50" s="42" t="n"/>
       <c r="F50" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -1984,13 +2007,13 @@
           <t>6. Cash Management</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C51" s="41" t="inlineStr">
         <is>
           <t>Build the cash flow forecast for months 1-3</t>
         </is>
       </c>
       <c r="D51" s="23" t="n"/>
-      <c r="E51" s="40" t="n"/>
+      <c r="E51" s="42" t="n"/>
       <c r="F51" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -2007,13 +2030,13 @@
           <t>6. Cash Management</t>
         </is>
       </c>
-      <c r="C52" s="9" t="inlineStr">
+      <c r="C52" s="41" t="inlineStr">
         <is>
           <t>Set the cash alert threshold</t>
         </is>
       </c>
       <c r="D52" s="23" t="n"/>
-      <c r="E52" s="40" t="n"/>
+      <c r="E52" s="42" t="n"/>
       <c r="F52" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -2021,22 +2044,22 @@
       </c>
       <c r="G52" s="23" t="n"/>
     </row>
-    <row r="53">
+    <row r="53" ht="30" customHeight="1">
       <c r="A53" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="31" t="inlineStr">
+      <c r="B53" s="43" t="inlineStr">
         <is>
           <t>7. Staff &amp; Employer Obligations</t>
         </is>
       </c>
-      <c r="C53" s="9" t="inlineStr">
+      <c r="C53" s="41" t="inlineStr">
         <is>
           <t>Register as an employer with your state (unemployment insurance account)</t>
         </is>
       </c>
       <c r="D53" s="32" t="n"/>
-      <c r="E53" s="41" t="n"/>
+      <c r="E53" s="44" t="n"/>
       <c r="F53" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -2044,22 +2067,22 @@
       </c>
       <c r="G53" s="32" t="n"/>
     </row>
-    <row r="54">
+    <row r="54" ht="30" customHeight="1">
       <c r="A54" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="31" t="inlineStr">
+      <c r="B54" s="43" t="inlineStr">
         <is>
           <t>7. Staff &amp; Employer Obligations</t>
         </is>
       </c>
-      <c r="C54" s="9" t="inlineStr">
+      <c r="C54" s="41" t="inlineStr">
         <is>
           <t>Set up the owner's pay: salary (S or C corp) or draws (LLC, sole proprietor)</t>
         </is>
       </c>
       <c r="D54" s="32" t="n"/>
-      <c r="E54" s="41" t="n"/>
+      <c r="E54" s="44" t="n"/>
       <c r="F54" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -2067,22 +2090,22 @@
       </c>
       <c r="G54" s="32" t="n"/>
     </row>
-    <row r="55">
+    <row r="55" ht="30" customHeight="1">
       <c r="A55" t="n">
         <v>51</v>
       </c>
-      <c r="B55" s="31" t="inlineStr">
+      <c r="B55" s="43" t="inlineStr">
         <is>
           <t>7. Staff &amp; Employer Obligations</t>
         </is>
       </c>
-      <c r="C55" s="9" t="inlineStr">
+      <c r="C55" s="41" t="inlineStr">
         <is>
           <t>Display the required federal and state labor law posters</t>
         </is>
       </c>
       <c r="D55" s="32" t="n"/>
-      <c r="E55" s="41" t="n"/>
+      <c r="E55" s="44" t="n"/>
       <c r="F55" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -2090,22 +2113,22 @@
       </c>
       <c r="G55" s="32" t="n"/>
     </row>
-    <row r="56">
+    <row r="56" ht="30" customHeight="1">
       <c r="A56" t="n">
         <v>52</v>
       </c>
-      <c r="B56" s="31" t="inlineStr">
+      <c r="B56" s="43" t="inlineStr">
         <is>
           <t>7. Staff &amp; Employer Obligations</t>
         </is>
       </c>
-      <c r="C56" s="9" t="inlineStr">
+      <c r="C56" s="41" t="inlineStr">
         <is>
           <t>Offer letters and handbook: pay rates, tip credit and overtime policy</t>
         </is>
       </c>
       <c r="D56" s="32" t="n"/>
-      <c r="E56" s="41" t="n"/>
+      <c r="E56" s="44" t="n"/>
       <c r="F56" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -2113,22 +2136,22 @@
       </c>
       <c r="G56" s="32" t="n"/>
     </row>
-    <row r="57">
+    <row r="57" ht="30" customHeight="1">
       <c r="A57" t="n">
         <v>53</v>
       </c>
-      <c r="B57" s="31" t="inlineStr">
+      <c r="B57" s="43" t="inlineStr">
         <is>
           <t>7. Staff &amp; Employer Obligations</t>
         </is>
       </c>
-      <c r="C57" s="9" t="inlineStr">
+      <c r="C57" s="41" t="inlineStr">
         <is>
           <t>Form I-9 and W-4 for every hire, plus new-hire reporting to the state</t>
         </is>
       </c>
       <c r="D57" s="32" t="n"/>
-      <c r="E57" s="41" t="n"/>
+      <c r="E57" s="44" t="n"/>
       <c r="F57" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -2136,22 +2159,22 @@
       </c>
       <c r="G57" s="32" t="n"/>
     </row>
-    <row r="58">
+    <row r="58" ht="30" customHeight="1">
       <c r="A58" t="n">
         <v>54</v>
       </c>
-      <c r="B58" s="31" t="inlineStr">
+      <c r="B58" s="43" t="inlineStr">
         <is>
           <t>7. Staff &amp; Employer Obligations</t>
         </is>
       </c>
-      <c r="C58" s="9" t="inlineStr">
+      <c r="C58" s="41" t="inlineStr">
         <is>
           <t>Time clock, payroll calendar and payroll tax deposits (Form 941)</t>
         </is>
       </c>
       <c r="D58" s="32" t="n"/>
-      <c r="E58" s="41" t="n"/>
+      <c r="E58" s="44" t="n"/>
       <c r="F58" s="25" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -2163,38 +2186,38 @@
       <c r="B59" s="17" t="n"/>
       <c r="C59" s="34" t="n"/>
       <c r="D59" s="32" t="n"/>
-      <c r="E59" s="41" t="n"/>
+      <c r="E59" s="44" t="n"/>
       <c r="F59" s="32" t="n"/>
       <c r="G59" s="32" t="n"/>
     </row>
     <row r="60">
       <c r="D60" s="32" t="n"/>
-      <c r="E60" s="41" t="n"/>
+      <c r="E60" s="44" t="n"/>
       <c r="F60" s="32" t="n"/>
       <c r="G60" s="32" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="20" t="n"/>
       <c r="D61" s="32" t="n"/>
-      <c r="E61" s="41" t="n"/>
+      <c r="E61" s="44" t="n"/>
       <c r="F61" s="32" t="n"/>
       <c r="G61" s="32" t="n"/>
     </row>
     <row r="62">
       <c r="D62" s="32" t="n"/>
-      <c r="E62" s="41" t="n"/>
+      <c r="E62" s="44" t="n"/>
       <c r="F62" s="32" t="n"/>
       <c r="G62" s="32" t="n"/>
     </row>
     <row r="63">
       <c r="D63" s="32" t="n"/>
-      <c r="E63" s="41" t="n"/>
+      <c r="E63" s="44" t="n"/>
       <c r="F63" s="32" t="n"/>
       <c r="G63" s="32" t="n"/>
     </row>
     <row r="64">
       <c r="D64" s="32" t="n"/>
-      <c r="E64" s="41" t="n"/>
+      <c r="E64" s="44" t="n"/>
       <c r="F64" s="32" t="n"/>
       <c r="G64" s="32" t="n"/>
     </row>
